--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -7302,7 +7302,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -19521,7 +19521,7 @@
           <t>B | 496呎 (2房)
 $1,294万
 $26,089/呎
-(25年-09月)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -18134,3486 +18001,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>滶晨 II - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>378 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>361 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1225呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 447呎 (2房)
-$1,139万
-$25,483/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,156万
-$25,523/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$1,260万
-$30,153/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 496呎 (2房)
-$1,492万
-$30,091/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 496呎 (2房)
-$1,270万
-$25,595/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,609万
-$27,369/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,390万
-$28,026/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,654万
-$27,988/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,170万
-$26,112/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,150万
-$25,382/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$1,159万
-$27,730/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 496呎 (2房)
-$1,319万
-$26,595/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,348万
-$27,283/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr"/>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="17" t="inlineStr"/>
-      <c r="M7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,601万
-$27,233/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,363万
-$27,488/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,645万
-$27,834/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,163万
-$25,964/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,144万
-$25,245/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,388万
-$27,493/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,371万
-$27,530/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,341万
-$27,146/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr"/>
-      <c r="K8" s="17" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,593万
-$27,097/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,378万
-$27,776/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,638万
-$27,709/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,178万
-$26,283/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,137万
-$25,106/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,440万
-$28,509/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,364万
-$27,394/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,283万
-$25,968/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,585万
-$26,963/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,372万
-$27,651/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,606万
-$27,176/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,117万
-$24,931/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,186万
-$26,181/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,436万
-$28,440/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,267万
-$25,444/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,277万
-$25,852/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,577万
-$26,827/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,345万
-$27,121/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,599万
-$27,054/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,111万
-$24,795/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,180万
-$26,038/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,330万
-$26,337/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,298万
-$26,074/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,233万
-$24,964/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr"/>
-      <c r="K11" s="17" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,570万
-$26,694/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,339万
-$27,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,592万
-$26,932/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,105万
-$24,658/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,173万
-$25,894/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,413万
-$27,980/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,344万
-$26,978/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,227万
-$24,840/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,562万
-$26,561/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,333万
-$26,879/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,565万
-$26,487/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,083万
-$24,174/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,064万
-$23,479/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,309万
-$25,923/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,248万
-$25,066/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,280万
-$25,915/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr"/>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,554万
-$26,429/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,327万
-$26,758/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,578万
-$26,692/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,038万
-$23,165/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,055万
-$23,294/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,299万
-$25,717/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,302万
-$26,149/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,215万
-$24,593/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr"/>
-      <c r="K14" s="17" t="inlineStr"/>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$6,061万
-$46,836/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M14" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$5,225万
-$45,123/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,449万
-$24,643/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,321万
-$26,639/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,570万
-$26,572/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,026万
-$22,891/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,047万
-$23,108/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,335万
-$26,440/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,256万
-$25,217/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,197万
-$24,229/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr"/>
-      <c r="K15" s="17" t="inlineStr"/>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4,827万
-$37,300/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,438万
-$24,459/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,315万
-$26,518/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,563万
-$26,453/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$998万
-$22,268/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,038万
-$22,923/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,278万
-$25,309/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,225万
-$24,594/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,174万
-$23,755/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr"/>
-      <c r="K16" s="17" t="inlineStr"/>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$5,795万
-$44,784/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,428万
-$24,277/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,310万
-$26,401/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,556万
-$26,335/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$991万
-$22,112/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,030万
-$22,742/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,214万
-$24,044/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,275万
-$25,608/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,128万
-$22,830/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr"/>
-      <c r="K17" s="17" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4,874万
-$42,091/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,417万
-$24,095/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,304万
-$26,282/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,531万
-$25,898/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$984万
-$21,958/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,009万
-$22,280/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,204万
-$23,851/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,208万
-$24,253/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,118万
-$22,626/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr"/>
-      <c r="K18" s="17" t="inlineStr"/>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4,609万
-$35,618/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4,029万
-$34,791/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,406万
-$23,918/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,306万
-$26,323/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,552万
-$26,257/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$977万
-$21,806/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,001万
-$22,104/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,271万
-$25,160/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,258万
-$25,253/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,108万
-$22,425/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr"/>
-      <c r="K19" s="17" t="inlineStr"/>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4,917万
-$38,000/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,466万
-$24,927/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,294万
-$26,089/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,529万
-$25,868/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$970万
-$21,654/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,004万
-$22,161/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,192万
-$23,608/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,249万
-$25,076/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,098万
-$22,225/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr"/>
-      <c r="K20" s="17" t="inlineStr"/>
-      <c r="L20" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$5,112万
-$39,505/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M20" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4,635万
-$40,022/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,455万
-$24,740/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,275万
-$25,700/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,515万
-$25,636/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$1,012万
-$22,578/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$996万
-$21,987/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,183万
-$23,422/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,183万
-$23,751/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,088万
-$22,026/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr"/>
-      <c r="K21" s="17" t="inlineStr"/>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4,428万
-$34,219/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$4,461万
-$38,522/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 588呎 (2房)
-$1,444万
-$24,556/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 496呎 (2房)
-$1,225万
-$24,700/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,502万
-$25,406/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$957万
-$21,355/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$988万
-$21,810/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,173万
-$23,236/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 498呎 (2房)
-$1,175万
-$23,586/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 494呎 (2房)
-$1,132万
-$22,921/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr"/>
-      <c r="K22" s="17" t="inlineStr"/>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 1294呎 (4+房)
-$4,859万
-$37,550/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M22" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 1158呎 (4+房)
-$3,972万
-$34,300/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,360万
-$23,213/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,315万
-$26,467/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,488万
-$25,181/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$998万
-$22,266/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$980万
-$21,638/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,164万
-$23,050/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,140万
-$22,713/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,071万
-$21,508/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,030万
-$21,460/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K23" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,152万
-$22,714/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,287万
-$29,400/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M23" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,209万
-$29,100/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,350万
-$23,039/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,243万
-$25,018/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,430万
-$24,200/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$992万
-$22,154/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$975万
-$21,530/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,158万
-$22,937/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,170万
-$23,307/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,119万
-$22,470/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,035万
-$21,558/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K24" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,146万
-$22,600/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="L24" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,264万
-$29,100/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,391万
-$31,501/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,338万
-$22,834/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,198万
-$24,115/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,493万
-$25,259/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$988万
-$22,045/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$970万
-$21,422/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,152万
-$22,822/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,164万
-$23,189/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,060万
-$21,293/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,068万
-$22,254/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K25" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,140万
-$22,487/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,241万
-$28,799/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M25" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,194万
-$28,900/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,326万
-$22,631/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,191万
-$23,972/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,413万
-$23,912/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$936万
-$20,891/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,014万
-$22,382/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,147万
-$22,709/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,179万
-$23,494/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,108万
-$22,247/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,063万
-$22,144/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,134万
-$22,375/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L26" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,217万
-$28,500/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="M26" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,155万
-$28,395/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,377万
-$23,502/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,244万
-$25,020/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,405万
-$23,770/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$931万
-$20,786/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,009万
-$22,272/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,141万
-$22,596/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,174万
-$23,376/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,050万
-$21,082/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,007万
-$20,983/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K27" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,129万
-$22,264/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,194万
-$28,201/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M27" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,221万
-$29,264/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,305万
-$22,271/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,177万
-$23,686/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,396万
-$23,628/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$927万
-$20,683/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$956万
-$21,104/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,135万
-$22,483/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,112万
-$22,153/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,097万
-$22,026/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J28" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,002万
-$20,879/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K28" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,123万
-$22,154/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L28" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,293万
-$29,474/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M28" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,273万
-$29,950/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,299万
-$22,160/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,157万
-$23,274/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,388万
-$23,486/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$922万
-$20,580/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$951万
-$21,000/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,130万
-$22,370/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,107万
-$22,044/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,040万
-$20,873/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$997万
-$20,775/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K29" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,118万
-$22,043/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,129万
-$27,361/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M29" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,121万
-$27,947/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,357万
-$23,152/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,139万
-$22,909/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,380万
-$23,347/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$963万
-$21,502/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$994万
-$21,938/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,124万
-$22,259/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,101万
-$21,934/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,034万
-$20,769/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$992万
-$20,673/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K30" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,168万
-$23,030/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L30" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,112万
-$27,144/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="M30" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,032万
-$26,771/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,286万
-$21,940/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,184万
-$23,817/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,372万
-$23,208/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$913万
-$20,375/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$942万
-$20,792/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,118万
-$22,149/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,096万
-$21,825/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,029万
-$20,667/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$987万
-$20,569/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K31" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,106万
-$21,824/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L31" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,095万
-$26,929/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M31" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,016万
-$26,557/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,279万
-$21,831/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,116万
-$22,459/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,363万
-$23,069/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$908万
-$20,275/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$937万
-$20,689/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,155万
-$22,865/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,090万
-$21,715/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,024万
-$20,562/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$982万
-$20,467/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K32" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,156万
-$22,801/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,078万
-$26,715/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="M32" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,000万
-$26,347/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,273万
-$21,722/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,105万
-$22,237/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,322万
-$22,372/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$904万
-$20,174/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$979万
-$21,614/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,107万
-$21,929/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,085万
-$21,608/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,070万
-$21,484/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$1,026万
-$21,383/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K33" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,150万
-$22,688/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,156万
-$27,719/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M33" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,075万
-$27,336/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,267万
-$21,614/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,094万
-$22,016/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,316万
-$22,261/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$899万
-$20,074/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$974万
-$21,508/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,102万
-$21,820/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H34" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,079万
-$21,500/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,014万
-$20,359/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J34" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$973万
-$20,265/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,144万
-$22,574/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L34" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,038万
-$26,189/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$1,960万
-$25,829/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,260万
-$21,507/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,055万
-$21,219/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,374万
-$23,257/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$895万
-$19,973/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$923万
-$20,380/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,096万
-$21,711/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,074万
-$21,394/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,009万
-$20,257/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J35" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$968万
-$20,162/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K35" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,085万
-$21,394/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,186万
-$28,091/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M35" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$1,945万
-$25,623/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,254万
-$21,399/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,102万
-$22,183/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,303万
-$22,041/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$890万
-$19,875/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$919万
-$20,280/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,091万
-$21,604/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,069万
-$21,287/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,004万
-$20,157/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$963万
-$20,062/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,079万
-$21,286/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L36" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,077万
-$26,700/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M36" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,163万
-$28,501/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,248万
-$21,294/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,110万
-$22,340/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,296万
-$21,931/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$886万
-$19,777/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$960万
-$21,185/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,140万
-$22,570/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,063万
-$21,181/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$999万
-$20,056/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J37" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$958万
-$19,962/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K37" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,074万
-$21,181/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L37" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,140万
-$27,500/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M37" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,148万
-$28,300/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>A | 586呎 (2房)
-$1,238万
-$21,125/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>B | 497呎 (2房)
-$1,049万
-$21,107/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,290万
-$21,821/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$879万
-$19,618/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$907万
-$20,018/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,077万
-$21,325/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,055万
-$21,012/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>H | 498呎 (2房)
-$1,040万
-$20,894/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J38" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$998万
-$20,794/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,065万
-$21,014/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L38" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,050万
-$26,350/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,269万
-$29,900/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr"/>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-$1,066万
-$20,939/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,347万
-$22,799/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 448呎 (2房)
-$872万
-$19,464/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$945万
-$20,852/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,068万
-$21,156/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
-        <is>
-          <t>G | 502呎 (2房)
-$1,046万
-$20,847/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I39" s="18" t="inlineStr">
-        <is>
-          <t>H | 505呎 (2房)
-$1,047万
-$20,727/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="J39" s="18" t="inlineStr">
-        <is>
-          <t>J | 480呎 (2房)
-$943万
-$19,648/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="K39" s="18" t="inlineStr">
-        <is>
-          <t>K | 507呎 (2房)
-$1,057万
-$20,846/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L39" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,150万
-$27,640/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M39" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,429万
-$32,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr"/>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-$1,110万
-$21,811/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>C | 591呎 (2房)
-$1,277万
-$21,604/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>D | 402呎 (2房)
-$1,199万
-$29,818/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>E | 407呎 (2房)
-$1,188万
-$29,194/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>F | 459呎 (2房)
-$1,249万
-$27,207/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>G | 455呎 (2房)
-$1,356万
-$29,798/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>H | 458呎 (2房)
-$1,319万
-$28,799/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J40" s="18" t="inlineStr">
-        <is>
-          <t>J | 433呎 (2房)
-$1,241万
-$28,656/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="inlineStr">
-        <is>
-          <t>K | 460呎 (2房)
-$1,329万
-$28,887/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="L40" s="18" t="inlineStr">
-        <is>
-          <t>P1 | 778呎 (3房)
-$2,473万
-$31,789/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="inlineStr">
-        <is>
-          <t>P2 | 759呎 (3房)
-$2,520万
-$33,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,91 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +137,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +218,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18001,4 +18172,3486 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1225呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 447呎 (2房)
+$1139万
+$25,483/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1156万
+$25,523/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$1260万
+$30,153/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 496呎 (2房)
+$1492万
+$30,091/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 496呎 (2房)
+$1270万
+$25,595/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1609万
+$27,369/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1390万
+$28,026/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1654万
+$27,988/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1170万
+$26,112/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1150万
+$25,382/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$1159万
+$27,730/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 496呎 (2房)
+$1319万
+$26,595/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1348万
+$27,283/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr"/>
+      <c r="K6" s="21" t="inlineStr"/>
+      <c r="L6" s="21" t="inlineStr"/>
+      <c r="M6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1601万
+$27,233/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1363万
+$27,488/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1645万
+$27,834/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1163万
+$25,964/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1144万
+$25,245/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1388万
+$27,493/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1371万
+$27,530/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1341万
+$27,146/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="21" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1593万
+$27,097/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1378万
+$27,776/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1638万
+$27,709/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1178万
+$26,283/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1137万
+$25,106/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1440万
+$28,509/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1364万
+$27,394/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1283万
+$25,968/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr"/>
+      <c r="K8" s="21" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1585万
+$26,963/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1372万
+$27,651/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1606万
+$27,176/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1117万
+$24,931/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1186万
+$26,181/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1436万
+$28,440/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1267万
+$25,444/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1277万
+$25,852/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr"/>
+      <c r="K9" s="21" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1577万
+$26,827/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1345万
+$27,121/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1599万
+$27,054/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1111万
+$24,795/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1180万
+$26,038/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1330万
+$26,337/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1298万
+$26,074/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1233万
+$24,964/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr"/>
+      <c r="K10" s="21" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1570万
+$26,694/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1339万
+$27,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1592万
+$26,932/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1105万
+$24,658/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1173万
+$25,894/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1413万
+$27,980/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1344万
+$26,978/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1227万
+$24,840/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr"/>
+      <c r="K11" s="21" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1562万
+$26,561/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1333万
+$26,879/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1565万
+$26,487/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1083万
+$24,174/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1064万
+$23,479/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1309万
+$25,923/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1248万
+$25,066/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1280万
+$25,915/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr"/>
+      <c r="K12" s="21" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1554万
+$26,429/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1327万
+$26,758/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1578万
+$26,692/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1038万
+$23,165/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1055万
+$23,294/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1299万
+$25,717/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1302万
+$26,149/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1215万
+$24,593/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr"/>
+      <c r="K13" s="21" t="inlineStr"/>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$6061万
+$46,836/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$5225万
+$45,123/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1449万
+$24,643/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1321万
+$26,639/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1570万
+$26,572/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1026万
+$22,891/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1047万
+$23,108/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1335万
+$26,440/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1256万
+$25,217/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1197万
+$24,229/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr"/>
+      <c r="K14" s="21" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4827万
+$37,300/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1438万
+$24,459/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1315万
+$26,518/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1563万
+$26,453/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$998万
+$22,268/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1038万
+$22,923/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1278万
+$25,309/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1225万
+$24,594/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1174万
+$23,755/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr"/>
+      <c r="K15" s="21" t="inlineStr"/>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$5795万
+$44,784/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1428万
+$24,277/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1310万
+$26,401/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1556万
+$26,335/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$991万
+$22,112/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1030万
+$22,742/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1214万
+$24,044/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1275万
+$25,608/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1128万
+$22,830/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr"/>
+      <c r="K16" s="21" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$4874万
+$42,091/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1417万
+$24,095/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1304万
+$26,282/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1531万
+$25,898/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$984万
+$21,958/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1009万
+$22,280/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1204万
+$23,851/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1208万
+$24,253/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1118万
+$22,626/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr"/>
+      <c r="K17" s="21" t="inlineStr"/>
+      <c r="L17" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4609万
+$35,618/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M17" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$4029万
+$34,791/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1406万
+$23,918/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1306万
+$26,323/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1552万
+$26,257/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$977万
+$21,806/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1001万
+$22,104/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1271万
+$25,160/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1258万
+$25,253/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1108万
+$22,425/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr"/>
+      <c r="K18" s="21" t="inlineStr"/>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4917万
+$38,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1466万
+$24,927/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1294万
+$26,089/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1529万
+$25,868/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$970万
+$21,654/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1004万
+$22,161/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1192万
+$23,608/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1249万
+$25,076/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1098万
+$22,225/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr"/>
+      <c r="K19" s="21" t="inlineStr"/>
+      <c r="L19" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$5112万
+$39,505/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$4635万
+$40,022/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1455万
+$24,740/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1275万
+$25,700/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1515万
+$25,636/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$1012万
+$22,578/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$996万
+$21,987/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1183万
+$23,422/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1183万
+$23,751/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1088万
+$22,026/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr"/>
+      <c r="K20" s="21" t="inlineStr"/>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4428万
+$34,219/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$4461万
+$38,522/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 588呎 (2房)
+$1444万
+$24,556/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 496呎 (2房)
+$1225万
+$24,700/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1502万
+$25,406/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$957万
+$21,355/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$988万
+$21,810/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1173万
+$23,236/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 498呎 (2房)
+$1175万
+$23,586/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 494呎 (2房)
+$1132万
+$22,921/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr"/>
+      <c r="K21" s="21" t="inlineStr"/>
+      <c r="L21" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 1294呎 (4+房)
+$4859万
+$37,550/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M21" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 1158呎 (4+房)
+$3972万
+$34,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1360万
+$23,213/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1315万
+$26,467/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1488万
+$25,181/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$998万
+$22,266/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$980万
+$21,638/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1164万
+$23,050/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1140万
+$22,713/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1071万
+$21,508/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1030万
+$21,460/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1152万
+$22,714/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2287万
+$29,400/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2209万
+$29,100/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1350万
+$23,039/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1243万
+$25,018/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1430万
+$24,200/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$992万
+$22,154/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$975万
+$21,530/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1158万
+$22,937/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1170万
+$23,307/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1119万
+$22,470/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1035万
+$21,558/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K23" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1146万
+$22,600/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2264万
+$29,100/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2391万
+$31,501/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1338万
+$22,834/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1198万
+$24,115/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1493万
+$25,259/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$988万
+$22,045/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$970万
+$21,422/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1152万
+$22,822/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1164万
+$23,189/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1060万
+$21,293/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1068万
+$22,254/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1140万
+$22,487/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2241万
+$28,799/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2194万
+$28,900/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1326万
+$22,631/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1191万
+$23,972/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1413万
+$23,912/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$936万
+$20,891/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1014万
+$22,382/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1147万
+$22,709/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1179万
+$23,494/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1108万
+$22,247/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1063万
+$22,144/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1134万
+$22,375/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2217万
+$28,500/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2155万
+$28,395/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1377万
+$23,502/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1244万
+$25,020/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1405万
+$23,770/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$931万
+$20,786/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1009万
+$22,272/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1141万
+$22,596/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1174万
+$23,376/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1050万
+$21,082/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1007万
+$20,983/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1129万
+$22,264/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2194万
+$28,201/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2221万
+$29,264/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1305万
+$22,271/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1177万
+$23,686/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1396万
+$23,628/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$927万
+$20,683/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$956万
+$21,104/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1135万
+$22,483/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1112万
+$22,153/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1097万
+$22,026/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1002万
+$20,879/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1123万
+$22,154/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2293万
+$29,474/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2273万
+$29,950/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1299万
+$22,160/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1157万
+$23,274/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1388万
+$23,486/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$922万
+$20,580/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$951万
+$21,000/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1130万
+$22,370/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1107万
+$22,044/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1040万
+$20,873/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$997万
+$20,775/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1118万
+$22,043/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2129万
+$27,361/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2121万
+$27,947/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1357万
+$23,152/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1139万
+$22,909/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1380万
+$23,347/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$963万
+$21,502/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$994万
+$21,938/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1124万
+$22,259/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1101万
+$21,934/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1034万
+$20,769/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$992万
+$20,673/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1168万
+$23,030/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2112万
+$27,144/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="M29" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2032万
+$26,771/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1286万
+$21,940/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1184万
+$23,817/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1372万
+$23,208/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$913万
+$20,375/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$942万
+$20,792/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1118万
+$22,149/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1096万
+$21,825/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1029万
+$20,667/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$987万
+$20,569/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1106万
+$21,824/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2095万
+$26,929/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2016万
+$26,557/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1279万
+$21,831/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1116万
+$22,459/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1363万
+$23,069/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$908万
+$20,275/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$937万
+$20,689/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1155万
+$22,865/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1090万
+$21,715/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1024万
+$20,562/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$982万
+$20,467/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1156万
+$22,801/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L31" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2078万
+$26,715/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="M31" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2000万
+$26,347/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1273万
+$21,722/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1105万
+$22,237/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1322万
+$22,372/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$904万
+$20,174/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$979万
+$21,614/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1107万
+$21,929/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1085万
+$21,608/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1070万
+$21,484/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$1026万
+$21,383/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1150万
+$22,688/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2156万
+$27,719/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2075万
+$27,336/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1267万
+$21,614/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1094万
+$22,016/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1316万
+$22,261/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$899万
+$20,074/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$974万
+$21,508/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1102万
+$21,820/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1079万
+$21,500/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1014万
+$20,359/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$973万
+$20,265/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1144万
+$22,574/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2038万
+$26,189/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="M33" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$1960万
+$25,829/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1260万
+$21,507/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1055万
+$21,219/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1374万
+$23,257/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$895万
+$19,973/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$923万
+$20,380/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1096万
+$21,711/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1074万
+$21,394/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1009万
+$20,257/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$968万
+$20,162/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1085万
+$21,394/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2186万
+$28,091/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$1945万
+$25,623/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1254万
+$21,399/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1102万
+$22,183/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1303万
+$22,041/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$890万
+$19,875/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$919万
+$20,280/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1091万
+$21,604/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1069万
+$21,287/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1004万
+$20,157/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$963万
+$20,062/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1079万
+$21,286/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2077万
+$26,700/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2163万
+$28,501/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1248万
+$21,294/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1110万
+$22,340/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1296万
+$21,931/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$886万
+$19,777/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$960万
+$21,185/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1140万
+$22,570/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1063万
+$21,181/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$999万
+$20,056/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$958万
+$19,962/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1074万
+$21,181/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2140万
+$27,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2148万
+$28,300/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>A | 586呎 (2房)
+$1238万
+$21,125/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B | 497呎 (2房)
+$1049万
+$21,107/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1290万
+$21,821/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$879万
+$19,618/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$907万
+$20,018/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1077万
+$21,325/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1055万
+$21,012/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>H | 498呎 (2房)
+$1040万
+$20,894/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$998万
+$20,794/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1065万
+$21,014/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2050万
+$26,350/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2269万
+$29,900/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+$1066万
+$20,939/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1347万
+$22,799/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 448呎 (2房)
+$872万
+$19,464/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$945万
+$20,852/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1068万
+$21,156/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>G | 502呎 (2房)
+$1046万
+$20,847/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>H | 505呎 (2房)
+$1047万
+$20,727/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>J | 480呎 (2房)
+$943万
+$19,648/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>K | 507呎 (2房)
+$1057万
+$20,846/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2150万
+$27,640/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2429万
+$32,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr"/>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+$1110万
+$21,811/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>C | 591呎 (2房)
+$1277万
+$21,604/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>D | 402呎 (2房)
+$1199万
+$29,818/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>E | 407呎 (2房)
+$1188万
+$29,194/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>F | 459呎 (2房)
+$1249万
+$27,207/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>G | 455呎 (2房)
+$1356万
+$29,798/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>H | 458呎 (2房)
+$1319万
+$28,799/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>J | 433呎 (2房)
+$1241万
+$28,656/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>K | 460呎 (2房)
+$1329万
+$28,887/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>P1 | 778呎 (3房)
+$2473万
+$31,789/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M39" s="22" t="inlineStr">
+        <is>
+          <t>P2 | 759呎 (3房)
+$2520万
+$33,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -645,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4895,12 +4895,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6081,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7399,12 +7399,12 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8585,12 +8585,12 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24485,7 +24485,7 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1225呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24687,7 +24687,7 @@
       <c r="L7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24695,7 +24695,7 @@
       <c r="M7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24776,7 +24776,7 @@
       <c r="L8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24784,7 +24784,7 @@
       <c r="M8" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24865,7 +24865,7 @@
       <c r="L9" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24873,7 +24873,7 @@
       <c r="M9" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24954,7 +24954,7 @@
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -24962,7 +24962,7 @@
       <c r="M10" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25043,7 +25043,7 @@
       <c r="L11" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25051,7 +25051,7 @@
       <c r="M11" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25132,7 +25132,7 @@
       <c r="L12" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25140,7 +25140,7 @@
       <c r="M12" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25318,7 +25318,7 @@
       <c r="M14" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25407,7 +25407,7 @@
       <c r="M15" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25488,7 +25488,7 @@
       <c r="L16" s="20" t="inlineStr">
         <is>
           <t>P1 | 1294呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>
@@ -25674,7 +25674,7 @@
       <c r="M18" s="20" t="inlineStr">
         <is>
           <t>P2 | 1158呎 (4+房)
-招标单位
+-
 -
 (暂停销售)</t>
         </is>

--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -24497,7 +24497,7 @@
           <t>D | 447呎 (2房)
 $1139万
 $25,483/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -24505,7 +24505,7 @@
           <t>E | 453呎 (2房)
 $1156万
 $25,523/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -24513,7 +24513,7 @@
           <t>F | 418呎 (1房)
 $1260万
 $30,153/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -24521,7 +24521,7 @@
           <t>G | 496呎 (2房)
 $1492万
 $30,091/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -24529,7 +24529,7 @@
           <t>H | 496呎 (2房)
 $1270万
 $25,595/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr"/>
@@ -24548,7 +24548,7 @@
           <t>A | 588呎 (2房)
 $1609万
 $27,369/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -24556,7 +24556,7 @@
           <t>B | 496呎 (2房)
 $1390万
 $28,026/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -24564,7 +24564,7 @@
           <t>C | 591呎 (2房)
 $1654万
 $27,988/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -24572,7 +24572,7 @@
           <t>D | 448呎 (2房)
 $1170万
 $26,112/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -24580,7 +24580,7 @@
           <t>E | 453呎 (2房)
 $1150万
 $25,382/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -24588,7 +24588,7 @@
           <t>F | 418呎 (1房)
 $1159万
 $27,730/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -24596,7 +24596,7 @@
           <t>G | 496呎 (2房)
 $1319万
 $26,595/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -24604,7 +24604,7 @@
           <t>H | 494呎 (2房)
 $1348万
 $27,283/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -24623,7 +24623,7 @@
           <t>A | 588呎 (2房)
 $1601万
 $27,233/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -24631,7 +24631,7 @@
           <t>B | 496呎 (2房)
 $1363万
 $27,488/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -24639,7 +24639,7 @@
           <t>C | 591呎 (2房)
 $1645万
 $27,834/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -24647,7 +24647,7 @@
           <t>D | 448呎 (2房)
 $1163万
 $25,964/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -24655,7 +24655,7 @@
           <t>E | 453呎 (2房)
 $1144万
 $25,245/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -24663,7 +24663,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,493/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -24671,7 +24671,7 @@
           <t>G | 498呎 (2房)
 $1371万
 $27,530/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -24679,7 +24679,7 @@
           <t>H | 494呎 (2房)
 $1341万
 $27,146/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr"/>
@@ -24712,7 +24712,7 @@
           <t>A | 588呎 (2房)
 $1593万
 $27,097/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24720,7 +24720,7 @@
           <t>B | 496呎 (2房)
 $1378万
 $27,776/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -24728,7 +24728,7 @@
           <t>C | 591呎 (2房)
 $1638万
 $27,709/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>D | 448呎 (2房)
 $1178万
 $26,283/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>E | 453呎 (2房)
 $1137万
 $25,106/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>F | 505呎 (2房)
 $1440万
 $28,509/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>G | 498呎 (2房)
 $1364万
 $27,394/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>H | 494呎 (2房)
 $1283万
 $25,968/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
           <t>A | 588呎 (2房)
 $1585万
 $26,963/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24809,7 +24809,7 @@
           <t>B | 496呎 (2房)
 $1372万
 $27,651/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -24817,7 +24817,7 @@
           <t>C | 591呎 (2房)
 $1606万
 $27,176/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -24825,7 +24825,7 @@
           <t>D | 448呎 (2房)
 $1117万
 $24,931/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -24833,7 +24833,7 @@
           <t>E | 453呎 (2房)
 $1186万
 $26,181/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -24841,7 +24841,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,440/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -24849,7 +24849,7 @@
           <t>G | 498呎 (2房)
 $1267万
 $25,444/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -24857,7 +24857,7 @@
           <t>H | 494呎 (2房)
 $1277万
 $25,852/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr"/>
@@ -24890,7 +24890,7 @@
           <t>A | 588呎 (2房)
 $1577万
 $26,827/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24898,7 +24898,7 @@
           <t>B | 496呎 (2房)
 $1345万
 $27,121/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -24906,7 +24906,7 @@
           <t>C | 591呎 (2房)
 $1599万
 $27,054/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -24914,7 +24914,7 @@
           <t>D | 448呎 (2房)
 $1111万
 $24,795/呎
-(25年-12月-15日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -24922,7 +24922,7 @@
           <t>E | 453呎 (2房)
 $1180万
 $26,038/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -24930,7 +24930,7 @@
           <t>F | 505呎 (2房)
 $1330万
 $26,337/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -24938,7 +24938,7 @@
           <t>G | 498呎 (2房)
 $1298万
 $26,074/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -24946,7 +24946,7 @@
           <t>H | 494呎 (2房)
 $1233万
 $24,964/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -24979,7 +24979,7 @@
           <t>A | 588呎 (2房)
 $1570万
 $26,694/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24987,7 +24987,7 @@
           <t>B | 496呎 (2房)
 $1339万
 $27,000/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -24995,7 +24995,7 @@
           <t>C | 591呎 (2房)
 $1592万
 $26,932/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -25003,7 +25003,7 @@
           <t>D | 448呎 (2房)
 $1105万
 $24,658/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -25011,7 +25011,7 @@
           <t>E | 453呎 (2房)
 $1173万
 $25,894/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -25019,7 +25019,7 @@
           <t>F | 505呎 (2房)
 $1413万
 $27,980/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -25027,7 +25027,7 @@
           <t>G | 498呎 (2房)
 $1344万
 $26,978/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -25035,7 +25035,7 @@
           <t>H | 494呎 (2房)
 $1227万
 $24,840/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr"/>
@@ -25068,7 +25068,7 @@
           <t>A | 588呎 (2房)
 $1562万
 $26,561/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -25076,7 +25076,7 @@
           <t>B | 496呎 (2房)
 $1333万
 $26,879/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -25084,7 +25084,7 @@
           <t>C | 591呎 (2房)
 $1565万
 $26,487/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -25092,7 +25092,7 @@
           <t>D | 448呎 (2房)
 $1083万
 $24,174/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -25100,7 +25100,7 @@
           <t>E | 453呎 (2房)
 $1064万
 $23,479/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -25108,7 +25108,7 @@
           <t>F | 505呎 (2房)
 $1309万
 $25,923/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -25116,7 +25116,7 @@
           <t>G | 498呎 (2房)
 $1248万
 $25,066/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -25124,7 +25124,7 @@
           <t>H | 494呎 (2房)
 $1280万
 $25,915/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr"/>
@@ -25157,7 +25157,7 @@
           <t>A | 588呎 (2房)
 $1554万
 $26,429/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -25165,7 +25165,7 @@
           <t>B | 496呎 (2房)
 $1327万
 $26,758/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>C | 591呎 (2房)
 $1578万
 $26,692/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>D | 448呎 (2房)
 $1038万
 $23,165/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>E | 453呎 (2房)
 $1055万
 $23,294/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>F | 505呎 (2房)
 $1299万
 $25,717/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>G | 498呎 (2房)
 $1302万
 $26,149/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>H | 494呎 (2房)
 $1215万
 $24,593/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr"/>
@@ -25223,7 +25223,7 @@
           <t>P1 | 1294呎 (4+房)
 $6061万
 $46,836/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -25231,7 +25231,7 @@
           <t>P2 | 1158呎 (4+房)
 $5225万
 $45,123/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
           <t>A | 588呎 (2房)
 $1449万
 $24,643/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25254,7 +25254,7 @@
           <t>B | 496呎 (2房)
 $1321万
 $26,639/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -25262,7 +25262,7 @@
           <t>C | 591呎 (2房)
 $1570万
 $26,572/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -25270,7 +25270,7 @@
           <t>D | 448呎 (2房)
 $1026万
 $22,891/呎
-(25年-09月-24日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -25278,7 +25278,7 @@
           <t>E | 453呎 (2房)
 $1047万
 $23,108/呎
-(25年-09月-24日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -25286,7 +25286,7 @@
           <t>F | 505呎 (2房)
 $1335万
 $26,440/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -25294,7 +25294,7 @@
           <t>G | 498呎 (2房)
 $1256万
 $25,217/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -25302,7 +25302,7 @@
           <t>H | 494呎 (2房)
 $1197万
 $24,229/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr"/>
@@ -25312,7 +25312,7 @@
           <t>P1 | 1294呎 (4+房)
 $4827万
 $37,300/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -25335,7 +25335,7 @@
           <t>A | 588呎 (2房)
 $1438万
 $24,459/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25343,7 +25343,7 @@
           <t>B | 496呎 (2房)
 $1315万
 $26,518/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25351,7 +25351,7 @@
           <t>C | 591呎 (2房)
 $1563万
 $26,453/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -25359,7 +25359,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,268/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -25367,7 +25367,7 @@
           <t>E | 453呎 (2房)
 $1038万
 $22,923/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -25375,7 +25375,7 @@
           <t>F | 505呎 (2房)
 $1278万
 $25,309/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -25383,7 +25383,7 @@
           <t>G | 498呎 (2房)
 $1225万
 $24,594/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -25391,7 +25391,7 @@
           <t>H | 494呎 (2房)
 $1174万
 $23,755/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr"/>
@@ -25401,7 +25401,7 @@
           <t>P1 | 1294呎 (4+房)
 $5795万
 $44,784/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -25424,7 +25424,7 @@
           <t>A | 588呎 (2房)
 $1428万
 $24,277/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25432,7 +25432,7 @@
           <t>B | 496呎 (2房)
 $1310万
 $26,401/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -25440,7 +25440,7 @@
           <t>C | 591呎 (2房)
 $1556万
 $26,335/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -25448,7 +25448,7 @@
           <t>D | 448呎 (2房)
 $991万
 $22,112/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -25456,7 +25456,7 @@
           <t>E | 453呎 (2房)
 $1030万
 $22,742/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -25464,7 +25464,7 @@
           <t>F | 505呎 (2房)
 $1214万
 $24,044/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -25472,7 +25472,7 @@
           <t>G | 498呎 (2房)
 $1275万
 $25,608/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -25480,7 +25480,7 @@
           <t>H | 494呎 (2房)
 $1128万
 $22,830/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr"/>
@@ -25498,7 +25498,7 @@
           <t>P2 | 1158呎 (4+房)
 $4874万
 $42,091/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -25513,7 +25513,7 @@
           <t>A | 588呎 (2房)
 $1417万
 $24,095/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25521,7 +25521,7 @@
           <t>B | 496呎 (2房)
 $1304万
 $26,282/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -25529,7 +25529,7 @@
           <t>C | 591呎 (2房)
 $1531万
 $25,898/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -25537,7 +25537,7 @@
           <t>D | 448呎 (2房)
 $984万
 $21,958/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -25545,7 +25545,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,280/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -25553,7 +25553,7 @@
           <t>F | 505呎 (2房)
 $1204万
 $23,851/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -25561,7 +25561,7 @@
           <t>G | 498呎 (2房)
 $1208万
 $24,253/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -25569,7 +25569,7 @@
           <t>H | 494呎 (2房)
 $1118万
 $22,626/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr"/>
@@ -25579,7 +25579,7 @@
           <t>P1 | 1294呎 (4+房)
 $4609万
 $35,618/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -25587,7 +25587,7 @@
           <t>P2 | 1158呎 (4+房)
 $4029万
 $34,791/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
           <t>A | 588呎 (2房)
 $1406万
 $23,918/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25610,7 +25610,7 @@
           <t>B | 496呎 (2房)
 $1306万
 $26,323/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -25618,7 +25618,7 @@
           <t>C | 591呎 (2房)
 $1552万
 $26,257/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -25626,7 +25626,7 @@
           <t>D | 448呎 (2房)
 $977万
 $21,806/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -25634,7 +25634,7 @@
           <t>E | 453呎 (2房)
 $1001万
 $22,104/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -25642,7 +25642,7 @@
           <t>F | 505呎 (2房)
 $1271万
 $25,160/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -25650,7 +25650,7 @@
           <t>G | 498呎 (2房)
 $1258万
 $25,253/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25658,7 +25658,7 @@
           <t>H | 494呎 (2房)
 $1108万
 $22,425/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr"/>
@@ -25668,7 +25668,7 @@
           <t>P1 | 1294呎 (4+房)
 $4917万
 $38,000/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -25691,7 +25691,7 @@
           <t>A | 588呎 (2房)
 $1466万
 $24,927/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25699,7 +25699,7 @@
           <t>B | 496呎 (2房)
 $1294万
 $26,089/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -25707,7 +25707,7 @@
           <t>C | 591呎 (2房)
 $1529万
 $25,868/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -25715,7 +25715,7 @@
           <t>D | 448呎 (2房)
 $970万
 $21,654/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -25723,7 +25723,7 @@
           <t>E | 453呎 (2房)
 $1004万
 $22,161/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -25731,7 +25731,7 @@
           <t>F | 505呎 (2房)
 $1192万
 $23,608/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>G | 498呎 (2房)
 $1249万
 $25,076/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25747,7 +25747,7 @@
           <t>H | 494呎 (2房)
 $1098万
 $22,225/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
           <t>P1 | 1294呎 (4+房)
 $5112万
 $39,505/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -25765,7 +25765,7 @@
           <t>P2 | 1158呎 (4+房)
 $4635万
 $40,022/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
           <t>A | 588呎 (2房)
 $1455万
 $24,740/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25788,7 +25788,7 @@
           <t>B | 496呎 (2房)
 $1275万
 $25,700/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -25796,7 +25796,7 @@
           <t>C | 591呎 (2房)
 $1515万
 $25,636/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -25804,7 +25804,7 @@
           <t>D | 448呎 (2房)
 $1012万
 $22,578/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -25812,7 +25812,7 @@
           <t>E | 453呎 (2房)
 $996万
 $21,987/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -25820,7 +25820,7 @@
           <t>F | 505呎 (2房)
 $1183万
 $23,422/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -25828,7 +25828,7 @@
           <t>G | 498呎 (2房)
 $1183万
 $23,751/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25836,7 +25836,7 @@
           <t>H | 494呎 (2房)
 $1088万
 $22,026/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr"/>
@@ -25846,7 +25846,7 @@
           <t>P1 | 1294呎 (4+房)
 $4428万
 $34,219/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -25854,7 +25854,7 @@
           <t>P2 | 1158呎 (4+房)
 $4461万
 $38,522/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
           <t>A | 588呎 (2房)
 $1444万
 $24,556/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25877,7 +25877,7 @@
           <t>B | 496呎 (2房)
 $1225万
 $24,700/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -25885,7 +25885,7 @@
           <t>C | 591呎 (2房)
 $1502万
 $25,406/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -25893,7 +25893,7 @@
           <t>D | 448呎 (2房)
 $957万
 $21,355/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -25901,7 +25901,7 @@
           <t>E | 453呎 (2房)
 $988万
 $21,810/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -25909,7 +25909,7 @@
           <t>F | 505呎 (2房)
 $1173万
 $23,236/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -25917,7 +25917,7 @@
           <t>G | 498呎 (2房)
 $1175万
 $23,586/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>H | 494呎 (2房)
 $1132万
 $22,921/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr"/>
@@ -25935,7 +25935,7 @@
           <t>P1 | 1294呎 (4+房)
 $4859万
 $37,550/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -25943,7 +25943,7 @@
           <t>P2 | 1158呎 (4+房)
 $3972万
 $34,300/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -25958,7 +25958,7 @@
           <t>A | 586呎 (2房)
 $1360万
 $23,213/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25966,7 +25966,7 @@
           <t>B | 497呎 (2房)
 $1315万
 $26,467/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -25974,7 +25974,7 @@
           <t>C | 591呎 (2房)
 $1488万
 $25,181/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -25982,7 +25982,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,266/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -25990,7 +25990,7 @@
           <t>E | 453呎 (2房)
 $980万
 $21,638/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -25998,7 +25998,7 @@
           <t>F | 505呎 (2房)
 $1164万
 $23,050/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -26006,7 +26006,7 @@
           <t>G | 502呎 (2房)
 $1140万
 $22,713/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -26014,7 +26014,7 @@
           <t>H | 498呎 (2房)
 $1071万
 $21,508/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>J | 480呎 (2房)
 $1030万
 $21,460/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>K | 507呎 (2房)
 $1152万
 $22,714/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -26038,7 +26038,7 @@
           <t>P1 | 778呎 (3房)
 $2287万
 $29,400/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -26046,7 +26046,7 @@
           <t>P2 | 759呎 (3房)
 $2209万
 $29,100/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26061,7 @@
           <t>A | 586呎 (2房)
 $1350万
 $23,039/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>B | 497呎 (2房)
 $1243万
 $25,018/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -26077,7 +26077,7 @@
           <t>C | 591呎 (2房)
 $1430万
 $24,200/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -26085,7 +26085,7 @@
           <t>D | 448呎 (2房)
 $992万
 $22,154/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -26093,7 +26093,7 @@
           <t>E | 453呎 (2房)
 $975万
 $21,530/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -26101,7 +26101,7 @@
           <t>F | 505呎 (2房)
 $1158万
 $22,937/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -26109,7 +26109,7 @@
           <t>G | 502呎 (2房)
 $1170万
 $23,307/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -26117,7 +26117,7 @@
           <t>H | 498呎 (2房)
 $1119万
 $22,470/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -26125,7 +26125,7 @@
           <t>J | 480呎 (2房)
 $1035万
 $21,558/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>K | 507呎 (2房)
 $1146万
 $22,600/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>P1 | 778呎 (3房)
 $2264万
 $29,100/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>P2 | 759呎 (3房)
 $2391万
 $31,501/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -26164,7 +26164,7 @@
           <t>A | 586呎 (2房)
 $1338万
 $22,834/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -26172,7 +26172,7 @@
           <t>B | 497呎 (2房)
 $1198万
 $24,115/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -26180,7 +26180,7 @@
           <t>C | 591呎 (2房)
 $1493万
 $25,259/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -26188,7 +26188,7 @@
           <t>D | 448呎 (2房)
 $988万
 $22,045/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -26196,7 +26196,7 @@
           <t>E | 453呎 (2房)
 $970万
 $21,422/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -26204,7 +26204,7 @@
           <t>F | 505呎 (2房)
 $1152万
 $22,822/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -26212,7 +26212,7 @@
           <t>G | 502呎 (2房)
 $1164万
 $23,189/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -26220,7 +26220,7 @@
           <t>H | 498呎 (2房)
 $1060万
 $21,293/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -26228,7 +26228,7 @@
           <t>J | 480呎 (2房)
 $1068万
 $22,254/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -26236,7 +26236,7 @@
           <t>K | 507呎 (2房)
 $1140万
 $22,487/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -26244,7 +26244,7 @@
           <t>P1 | 778呎 (3房)
 $2241万
 $28,799/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -26252,7 +26252,7 @@
           <t>P2 | 759呎 (3房)
 $2194万
 $28,900/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -26267,7 +26267,7 @@
           <t>A | 586呎 (2房)
 $1326万
 $22,631/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>B | 497呎 (2房)
 $1191万
 $23,972/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>C | 591呎 (2房)
 $1413万
 $23,912/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -26291,7 +26291,7 @@
           <t>D | 448呎 (2房)
 $936万
 $20,891/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -26299,7 +26299,7 @@
           <t>E | 453呎 (2房)
 $1014万
 $22,382/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -26307,7 +26307,7 @@
           <t>F | 505呎 (2房)
 $1147万
 $22,709/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -26315,7 +26315,7 @@
           <t>G | 502呎 (2房)
 $1179万
 $23,494/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -26323,7 +26323,7 @@
           <t>H | 498呎 (2房)
 $1108万
 $22,247/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -26331,7 +26331,7 @@
           <t>J | 480呎 (2房)
 $1063万
 $22,144/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -26339,7 +26339,7 @@
           <t>K | 507呎 (2房)
 $1134万
 $22,375/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -26347,7 +26347,7 @@
           <t>P1 | 778呎 (3房)
 $2217万
 $28,500/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -26355,7 +26355,7 @@
           <t>P2 | 759呎 (3房)
 $2155万
 $28,395/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -26370,7 +26370,7 @@
           <t>A | 586呎 (2房)
 $1377万
 $23,502/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>B | 497呎 (2房)
 $1244万
 $25,020/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>C | 591呎 (2房)
 $1405万
 $23,770/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>D | 448呎 (2房)
 $931万
 $20,786/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,272/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>F | 505呎 (2房)
 $1141万
 $22,596/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -26418,7 +26418,7 @@
           <t>G | 502呎 (2房)
 $1174万
 $23,376/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -26426,7 +26426,7 @@
           <t>H | 498呎 (2房)
 $1050万
 $21,082/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -26434,7 +26434,7 @@
           <t>J | 480呎 (2房)
 $1007万
 $20,983/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -26442,7 +26442,7 @@
           <t>K | 507呎 (2房)
 $1129万
 $22,264/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -26450,7 +26450,7 @@
           <t>P1 | 778呎 (3房)
 $2194万
 $28,201/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -26458,7 +26458,7 @@
           <t>P2 | 759呎 (3房)
 $2221万
 $29,264/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
           <t>A | 586呎 (2房)
 $1305万
 $22,271/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>B | 497呎 (2房)
 $1177万
 $23,686/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>C | 591呎 (2房)
 $1396万
 $23,628/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>D | 448呎 (2房)
 $927万
 $20,683/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>E | 453呎 (2房)
 $956万
 $21,104/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>F | 505呎 (2房)
 $1135万
 $22,483/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>G | 502呎 (2房)
 $1112万
 $22,153/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>H | 498呎 (2房)
 $1097万
 $22,026/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>J | 480呎 (2房)
 $1002万
 $20,879/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -26545,7 +26545,7 @@
           <t>K | 507呎 (2房)
 $1123万
 $22,154/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -26553,7 +26553,7 @@
           <t>P1 | 778呎 (3房)
 $2293万
 $29,474/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -26561,7 +26561,7 @@
           <t>P2 | 759呎 (3房)
 $2273万
 $29,950/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
           <t>A | 586呎 (2房)
 $1299万
 $22,160/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>B | 497呎 (2房)
 $1157万
 $23,274/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>C | 591呎 (2房)
 $1388万
 $23,486/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>D | 448呎 (2房)
 $922万
 $20,580/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>E | 453呎 (2房)
 $951万
 $21,000/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>F | 505呎 (2房)
 $1130万
 $22,370/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>G | 502呎 (2房)
 $1107万
 $22,044/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,873/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>J | 480呎 (2房)
 $997万
 $20,775/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>K | 507呎 (2房)
 $1118万
 $22,043/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P1 | 778呎 (3房)
 $2129万
 $27,361/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>P2 | 759呎 (3房)
 $2121万
 $27,947/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 586呎 (2房)
 $1357万
 $23,152/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 497呎 (2房)
 $1139万
 $22,909/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 591呎 (2房)
 $1380万
 $23,347/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 448呎 (2房)
 $963万
 $21,502/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 453呎 (2房)
 $994万
 $21,938/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 505呎 (2房)
 $1124万
 $22,259/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 502呎 (2房)
 $1101万
 $21,934/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 498呎 (2房)
 $1034万
 $20,769/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 480呎 (2房)
 $992万
 $20,673/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 507呎 (2房)
 $1168万
 $23,030/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>P1 | 778呎 (3房)
 $2112万
 $27,144/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>P2 | 759呎 (3房)
 $2032万
 $26,771/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -26782,7 +26782,7 @@
           <t>A | 586呎 (2房)
 $1286万
 $21,940/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -26790,7 +26790,7 @@
           <t>B | 497呎 (2房)
 $1184万
 $23,817/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -26798,7 +26798,7 @@
           <t>C | 591呎 (2房)
 $1372万
 $23,208/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -26806,7 +26806,7 @@
           <t>D | 448呎 (2房)
 $913万
 $20,375/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>E | 453呎 (2房)
 $942万
 $20,792/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>F | 505呎 (2房)
 $1118万
 $22,149/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>G | 502呎 (2房)
 $1096万
 $21,825/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>H | 498呎 (2房)
 $1029万
 $20,667/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>J | 480呎 (2房)
 $987万
 $20,569/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>K | 507呎 (2房)
 $1106万
 $21,824/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>P1 | 778呎 (3房)
 $2095万
 $26,929/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>P2 | 759呎 (3房)
 $2016万
 $26,557/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26885,7 @@
           <t>A | 586呎 (2房)
 $1279万
 $21,831/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -26893,7 +26893,7 @@
           <t>B | 497呎 (2房)
 $1116万
 $22,459/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -26901,7 +26901,7 @@
           <t>C | 591呎 (2房)
 $1363万
 $23,069/呎
-(25年-09月-18日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -26909,7 +26909,7 @@
           <t>D | 448呎 (2房)
 $908万
 $20,275/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -26917,7 +26917,7 @@
           <t>E | 453呎 (2房)
 $937万
 $20,689/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -26925,7 +26925,7 @@
           <t>F | 505呎 (2房)
 $1155万
 $22,865/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -26933,7 +26933,7 @@
           <t>G | 502呎 (2房)
 $1090万
 $21,715/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>H | 498呎 (2房)
 $1024万
 $20,562/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>J | 480呎 (2房)
 $982万
 $20,467/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>K | 507呎 (2房)
 $1156万
 $22,801/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>P1 | 778呎 (3房)
 $2078万
 $26,715/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>P2 | 759呎 (3房)
 $2000万
 $26,347/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -26988,7 +26988,7 @@
           <t>A | 586呎 (2房)
 $1273万
 $21,722/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -26996,7 +26996,7 @@
           <t>B | 497呎 (2房)
 $1105万
 $22,237/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -27004,7 +27004,7 @@
           <t>C | 591呎 (2房)
 $1322万
 $22,372/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27012,7 +27012,7 @@
           <t>D | 448呎 (2房)
 $904万
 $20,174/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -27020,7 +27020,7 @@
           <t>E | 453呎 (2房)
 $979万
 $21,614/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -27028,7 +27028,7 @@
           <t>F | 505呎 (2房)
 $1107万
 $21,929/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -27036,7 +27036,7 @@
           <t>G | 502呎 (2房)
 $1085万
 $21,608/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -27044,7 +27044,7 @@
           <t>H | 498呎 (2房)
 $1070万
 $21,484/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -27052,7 +27052,7 @@
           <t>J | 480呎 (2房)
 $1026万
 $21,383/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -27060,7 +27060,7 @@
           <t>K | 507呎 (2房)
 $1150万
 $22,688/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>P1 | 778呎 (3房)
 $2156万
 $27,719/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>P2 | 759呎 (3房)
 $2075万
 $27,336/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
           <t>A | 586呎 (2房)
 $1267万
 $21,614/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -27099,7 +27099,7 @@
           <t>B | 497呎 (2房)
 $1094万
 $22,016/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -27107,7 +27107,7 @@
           <t>C | 591呎 (2房)
 $1316万
 $22,261/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27115,7 +27115,7 @@
           <t>D | 448呎 (2房)
 $899万
 $20,074/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27123,7 +27123,7 @@
           <t>E | 453呎 (2房)
 $974万
 $21,508/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -27131,7 +27131,7 @@
           <t>F | 505呎 (2房)
 $1102万
 $21,820/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -27139,7 +27139,7 @@
           <t>G | 502呎 (2房)
 $1079万
 $21,500/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -27147,7 +27147,7 @@
           <t>H | 498呎 (2房)
 $1014万
 $20,359/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -27155,7 +27155,7 @@
           <t>J | 480呎 (2房)
 $973万
 $20,265/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -27163,7 +27163,7 @@
           <t>K | 507呎 (2房)
 $1144万
 $22,574/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -27171,7 +27171,7 @@
           <t>P1 | 778呎 (3房)
 $2038万
 $26,189/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -27179,7 +27179,7 @@
           <t>P2 | 759呎 (3房)
 $1960万
 $25,829/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
           <t>A | 586呎 (2房)
 $1260万
 $21,507/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -27202,7 +27202,7 @@
           <t>B | 497呎 (2房)
 $1055万
 $21,219/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -27210,7 +27210,7 @@
           <t>C | 591呎 (2房)
 $1374万
 $23,257/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27218,7 +27218,7 @@
           <t>D | 448呎 (2房)
 $895万
 $19,973/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27226,7 +27226,7 @@
           <t>E | 453呎 (2房)
 $923万
 $20,380/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -27234,7 +27234,7 @@
           <t>F | 505呎 (2房)
 $1096万
 $21,711/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
@@ -27242,7 +27242,7 @@
           <t>G | 502呎 (2房)
 $1074万
 $21,394/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -27250,7 +27250,7 @@
           <t>H | 498呎 (2房)
 $1009万
 $20,257/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -27258,7 +27258,7 @@
           <t>J | 480呎 (2房)
 $968万
 $20,162/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -27266,7 +27266,7 @@
           <t>K | 507呎 (2房)
 $1085万
 $21,394/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -27274,7 +27274,7 @@
           <t>P1 | 778呎 (3房)
 $2186万
 $28,091/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -27282,7 +27282,7 @@
           <t>P2 | 759呎 (3房)
 $1945万
 $25,623/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
           <t>A | 586呎 (2房)
 $1254万
 $21,399/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -27305,7 +27305,7 @@
           <t>B | 497呎 (2房)
 $1102万
 $22,183/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -27313,7 +27313,7 @@
           <t>C | 591呎 (2房)
 $1303万
 $22,041/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -27321,7 +27321,7 @@
           <t>D | 448呎 (2房)
 $890万
 $19,875/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -27329,7 +27329,7 @@
           <t>E | 453呎 (2房)
 $919万
 $20,280/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -27337,7 +27337,7 @@
           <t>F | 505呎 (2房)
 $1091万
 $21,604/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -27345,7 +27345,7 @@
           <t>G | 502呎 (2房)
 $1069万
 $21,287/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -27353,7 +27353,7 @@
           <t>H | 498呎 (2房)
 $1004万
 $20,157/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -27361,7 +27361,7 @@
           <t>J | 480呎 (2房)
 $963万
 $20,062/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -27369,7 +27369,7 @@
           <t>K | 507呎 (2房)
 $1079万
 $21,286/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -27377,7 +27377,7 @@
           <t>P1 | 778呎 (3房)
 $2077万
 $26,700/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -27385,7 +27385,7 @@
           <t>P2 | 759呎 (3房)
 $2163万
 $28,501/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
           <t>A | 586呎 (2房)
 $1248万
 $21,294/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -27408,7 +27408,7 @@
           <t>B | 497呎 (2房)
 $1110万
 $22,340/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -27416,7 +27416,7 @@
           <t>C | 591呎 (2房)
 $1296万
 $21,931/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -27424,7 +27424,7 @@
           <t>D | 448呎 (2房)
 $886万
 $19,777/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -27432,7 +27432,7 @@
           <t>E | 453呎 (2房)
 $960万
 $21,185/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -27440,7 +27440,7 @@
           <t>F | 505呎 (2房)
 $1140万
 $22,570/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -27448,7 +27448,7 @@
           <t>G | 502呎 (2房)
 $1063万
 $21,181/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -27456,7 +27456,7 @@
           <t>H | 498呎 (2房)
 $999万
 $20,056/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>J | 480呎 (2房)
 $958万
 $19,962/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -27472,7 +27472,7 @@
           <t>K | 507呎 (2房)
 $1074万
 $21,181/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -27480,7 +27480,7 @@
           <t>P1 | 778呎 (3房)
 $2140万
 $27,500/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -27488,7 +27488,7 @@
           <t>P2 | 759呎 (3房)
 $2148万
 $28,300/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
           <t>A | 586呎 (2房)
 $1238万
 $21,125/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>B | 497呎 (2房)
 $1049万
 $21,107/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>C | 591呎 (2房)
 $1290万
 $21,821/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>D | 448呎 (2房)
 $879万
 $19,618/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>E | 453呎 (2房)
 $907万
 $20,018/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>F | 505呎 (2房)
 $1077万
 $21,325/呎
-(25年-09月-04日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -27551,7 +27551,7 @@
           <t>G | 502呎 (2房)
 $1055万
 $21,012/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -27559,7 +27559,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,894/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -27567,7 +27567,7 @@
           <t>J | 480呎 (2房)
 $998万
 $20,794/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -27575,7 +27575,7 @@
           <t>K | 507呎 (2房)
 $1065万
 $21,014/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -27583,7 +27583,7 @@
           <t>P1 | 778呎 (3房)
 $2050万
 $26,350/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -27591,7 +27591,7 @@
           <t>P2 | 759呎 (3房)
 $2269万
 $29,900/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27607,7 @@
           <t>B | 509呎 (2房)
 $1066万
 $20,939/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -27615,7 +27615,7 @@
           <t>C | 591呎 (2房)
 $1347万
 $22,799/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -27623,7 +27623,7 @@
           <t>D | 448呎 (2房)
 $872万
 $19,464/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -27631,7 +27631,7 @@
           <t>E | 453呎 (2房)
 $945万
 $20,852/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -27639,7 +27639,7 @@
           <t>F | 505呎 (2房)
 $1068万
 $21,156/呎
-(25年-09月-24日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">
@@ -27647,7 +27647,7 @@
           <t>G | 502呎 (2房)
 $1046万
 $20,847/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -27655,7 +27655,7 @@
           <t>H | 505呎 (2房)
 $1047万
 $20,727/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -27663,7 +27663,7 @@
           <t>J | 480呎 (2房)
 $943万
 $19,648/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
@@ -27671,7 +27671,7 @@
           <t>K | 507呎 (2房)
 $1057万
 $20,846/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
@@ -27679,7 +27679,7 @@
           <t>P1 | 778呎 (3房)
 $2150万
 $27,640/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
@@ -27687,7 +27687,7 @@
           <t>P2 | 759呎 (3房)
 $2429万
 $32,000/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
           <t>B | 509呎 (2房)
 $1110万
 $21,811/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 591呎 (2房)
 $1277万
 $21,604/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 402呎 (2房)
 $1199万
 $29,818/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 407呎 (2房)
 $1188万
 $29,194/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 459呎 (2房)
 $1249万
 $27,207/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H39" s="22" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 455呎 (2房)
 $1356万
 $29,798/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 458呎 (2房)
 $1319万
 $28,799/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 433呎 (2房)
 $1241万
 $28,656/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="K39" s="22" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 460呎 (2房)
 $1329万
 $28,887/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>P1 | 778呎 (3房)
 $2473万
 $31,789/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M39" s="22" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>P2 | 759呎 (3房)
 $2520万
 $33,200/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-滶晨 II.xlsx
@@ -24497,7 +24497,7 @@
           <t>D | 447呎 (2房)
 $1139万
 $25,483/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -24505,7 +24505,7 @@
           <t>E | 453呎 (2房)
 $1156万
 $25,523/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -24513,7 +24513,7 @@
           <t>F | 418呎 (1房)
 $1260万
 $30,153/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -24521,7 +24521,7 @@
           <t>G | 496呎 (2房)
 $1492万
 $30,091/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -24529,7 +24529,7 @@
           <t>H | 496呎 (2房)
 $1270万
 $25,595/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr"/>
@@ -24548,7 +24548,7 @@
           <t>A | 588呎 (2房)
 $1609万
 $27,369/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -24556,7 +24556,7 @@
           <t>B | 496呎 (2房)
 $1390万
 $28,026/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -24564,7 +24564,7 @@
           <t>C | 591呎 (2房)
 $1654万
 $27,988/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -24572,7 +24572,7 @@
           <t>D | 448呎 (2房)
 $1170万
 $26,112/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -24580,7 +24580,7 @@
           <t>E | 453呎 (2房)
 $1150万
 $25,382/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -24588,7 +24588,7 @@
           <t>F | 418呎 (1房)
 $1159万
 $27,730/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -24596,7 +24596,7 @@
           <t>G | 496呎 (2房)
 $1319万
 $26,595/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -24604,7 +24604,7 @@
           <t>H | 494呎 (2房)
 $1348万
 $27,283/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -24623,7 +24623,7 @@
           <t>A | 588呎 (2房)
 $1601万
 $27,233/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -24631,7 +24631,7 @@
           <t>B | 496呎 (2房)
 $1363万
 $27,488/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -24639,7 +24639,7 @@
           <t>C | 591呎 (2房)
 $1645万
 $27,834/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -24647,7 +24647,7 @@
           <t>D | 448呎 (2房)
 $1163万
 $25,964/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -24655,7 +24655,7 @@
           <t>E | 453呎 (2房)
 $1144万
 $25,245/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -24663,7 +24663,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,493/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -24671,7 +24671,7 @@
           <t>G | 498呎 (2房)
 $1371万
 $27,530/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -24679,7 +24679,7 @@
           <t>H | 494呎 (2房)
 $1341万
 $27,146/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr"/>
@@ -24712,7 +24712,7 @@
           <t>A | 588呎 (2房)
 $1593万
 $27,097/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24720,7 +24720,7 @@
           <t>B | 496呎 (2房)
 $1378万
 $27,776/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -24728,7 +24728,7 @@
           <t>C | 591呎 (2房)
 $1638万
 $27,709/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>D | 448呎 (2房)
 $1178万
 $26,283/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>E | 453呎 (2房)
 $1137万
 $25,106/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>F | 505呎 (2房)
 $1440万
 $28,509/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>G | 498呎 (2房)
 $1364万
 $27,394/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>H | 494呎 (2房)
 $1283万
 $25,968/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
           <t>A | 588呎 (2房)
 $1585万
 $26,963/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24809,7 +24809,7 @@
           <t>B | 496呎 (2房)
 $1372万
 $27,651/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -24817,7 +24817,7 @@
           <t>C | 591呎 (2房)
 $1606万
 $27,176/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -24825,7 +24825,7 @@
           <t>D | 448呎 (2房)
 $1117万
 $24,931/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -24833,7 +24833,7 @@
           <t>E | 453呎 (2房)
 $1186万
 $26,181/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -24841,7 +24841,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,440/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -24849,7 +24849,7 @@
           <t>G | 498呎 (2房)
 $1267万
 $25,444/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -24857,7 +24857,7 @@
           <t>H | 494呎 (2房)
 $1277万
 $25,852/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr"/>
@@ -24890,7 +24890,7 @@
           <t>A | 588呎 (2房)
 $1577万
 $26,827/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24898,7 +24898,7 @@
           <t>B | 496呎 (2房)
 $1345万
 $27,121/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -24906,7 +24906,7 @@
           <t>C | 591呎 (2房)
 $1599万
 $27,054/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -24914,7 +24914,7 @@
           <t>D | 448呎 (2房)
 $1111万
 $24,795/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -24922,7 +24922,7 @@
           <t>E | 453呎 (2房)
 $1180万
 $26,038/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -24930,7 +24930,7 @@
           <t>F | 505呎 (2房)
 $1330万
 $26,337/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -24938,7 +24938,7 @@
           <t>G | 498呎 (2房)
 $1298万
 $26,074/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -24946,7 +24946,7 @@
           <t>H | 494呎 (2房)
 $1233万
 $24,964/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -24979,7 +24979,7 @@
           <t>A | 588呎 (2房)
 $1570万
 $26,694/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24987,7 +24987,7 @@
           <t>B | 496呎 (2房)
 $1339万
 $27,000/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -24995,7 +24995,7 @@
           <t>C | 591呎 (2房)
 $1592万
 $26,932/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -25003,7 +25003,7 @@
           <t>D | 448呎 (2房)
 $1105万
 $24,658/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -25011,7 +25011,7 @@
           <t>E | 453呎 (2房)
 $1173万
 $25,894/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -25019,7 +25019,7 @@
           <t>F | 505呎 (2房)
 $1413万
 $27,980/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -25027,7 +25027,7 @@
           <t>G | 498呎 (2房)
 $1344万
 $26,978/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -25035,7 +25035,7 @@
           <t>H | 494呎 (2房)
 $1227万
 $24,840/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr"/>
@@ -25068,7 +25068,7 @@
           <t>A | 588呎 (2房)
 $1562万
 $26,561/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -25076,7 +25076,7 @@
           <t>B | 496呎 (2房)
 $1333万
 $26,879/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -25084,7 +25084,7 @@
           <t>C | 591呎 (2房)
 $1565万
 $26,487/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -25092,7 +25092,7 @@
           <t>D | 448呎 (2房)
 $1083万
 $24,174/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -25100,7 +25100,7 @@
           <t>E | 453呎 (2房)
 $1064万
 $23,479/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -25108,7 +25108,7 @@
           <t>F | 505呎 (2房)
 $1309万
 $25,923/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -25116,7 +25116,7 @@
           <t>G | 498呎 (2房)
 $1248万
 $25,066/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -25124,7 +25124,7 @@
           <t>H | 494呎 (2房)
 $1280万
 $25,915/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr"/>
@@ -25157,7 +25157,7 @@
           <t>A | 588呎 (2房)
 $1554万
 $26,429/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -25165,7 +25165,7 @@
           <t>B | 496呎 (2房)
 $1327万
 $26,758/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>C | 591呎 (2房)
 $1578万
 $26,692/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>D | 448呎 (2房)
 $1038万
 $23,165/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>E | 453呎 (2房)
 $1055万
 $23,294/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>F | 505呎 (2房)
 $1299万
 $25,717/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>G | 498呎 (2房)
 $1302万
 $26,149/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>H | 494呎 (2房)
 $1215万
 $24,593/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr"/>
@@ -25223,7 +25223,7 @@
           <t>P1 | 1294呎 (4+房)
 $6061万
 $46,836/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -25231,7 +25231,7 @@
           <t>P2 | 1158呎 (4+房)
 $5225万
 $45,123/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
           <t>A | 588呎 (2房)
 $1449万
 $24,643/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25254,7 +25254,7 @@
           <t>B | 496呎 (2房)
 $1321万
 $26,639/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -25262,7 +25262,7 @@
           <t>C | 591呎 (2房)
 $1570万
 $26,572/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -25270,7 +25270,7 @@
           <t>D | 448呎 (2房)
 $1026万
 $22,891/呎
-(25年-09月)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -25278,7 +25278,7 @@
           <t>E | 453呎 (2房)
 $1047万
 $23,108/呎
-(25年-09月)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -25286,7 +25286,7 @@
           <t>F | 505呎 (2房)
 $1335万
 $26,440/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -25294,7 +25294,7 @@
           <t>G | 498呎 (2房)
 $1256万
 $25,217/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -25302,7 +25302,7 @@
           <t>H | 494呎 (2房)
 $1197万
 $24,229/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr"/>
@@ -25312,7 +25312,7 @@
           <t>P1 | 1294呎 (4+房)
 $4827万
 $37,300/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -25335,7 +25335,7 @@
           <t>A | 588呎 (2房)
 $1438万
 $24,459/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25343,7 +25343,7 @@
           <t>B | 496呎 (2房)
 $1315万
 $26,518/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25351,7 +25351,7 @@
           <t>C | 591呎 (2房)
 $1563万
 $26,453/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -25359,7 +25359,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,268/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -25367,7 +25367,7 @@
           <t>E | 453呎 (2房)
 $1038万
 $22,923/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -25375,7 +25375,7 @@
           <t>F | 505呎 (2房)
 $1278万
 $25,309/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -25383,7 +25383,7 @@
           <t>G | 498呎 (2房)
 $1225万
 $24,594/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -25391,7 +25391,7 @@
           <t>H | 494呎 (2房)
 $1174万
 $23,755/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr"/>
@@ -25401,7 +25401,7 @@
           <t>P1 | 1294呎 (4+房)
 $5795万
 $44,784/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -25424,7 +25424,7 @@
           <t>A | 588呎 (2房)
 $1428万
 $24,277/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25432,7 +25432,7 @@
           <t>B | 496呎 (2房)
 $1310万
 $26,401/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -25440,7 +25440,7 @@
           <t>C | 591呎 (2房)
 $1556万
 $26,335/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -25448,7 +25448,7 @@
           <t>D | 448呎 (2房)
 $991万
 $22,112/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -25456,7 +25456,7 @@
           <t>E | 453呎 (2房)
 $1030万
 $22,742/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -25464,7 +25464,7 @@
           <t>F | 505呎 (2房)
 $1214万
 $24,044/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -25472,7 +25472,7 @@
           <t>G | 498呎 (2房)
 $1275万
 $25,608/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -25480,7 +25480,7 @@
           <t>H | 494呎 (2房)
 $1128万
 $22,830/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr"/>
@@ -25498,7 +25498,7 @@
           <t>P2 | 1158呎 (4+房)
 $4874万
 $42,091/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -25513,7 +25513,7 @@
           <t>A | 588呎 (2房)
 $1417万
 $24,095/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25521,7 +25521,7 @@
           <t>B | 496呎 (2房)
 $1304万
 $26,282/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -25529,7 +25529,7 @@
           <t>C | 591呎 (2房)
 $1531万
 $25,898/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -25537,7 +25537,7 @@
           <t>D | 448呎 (2房)
 $984万
 $21,958/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -25545,7 +25545,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,280/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -25553,7 +25553,7 @@
           <t>F | 505呎 (2房)
 $1204万
 $23,851/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -25561,7 +25561,7 @@
           <t>G | 498呎 (2房)
 $1208万
 $24,253/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -25569,7 +25569,7 @@
           <t>H | 494呎 (2房)
 $1118万
 $22,626/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr"/>
@@ -25579,7 +25579,7 @@
           <t>P1 | 1294呎 (4+房)
 $4609万
 $35,618/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -25587,7 +25587,7 @@
           <t>P2 | 1158呎 (4+房)
 $4029万
 $34,791/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
           <t>A | 588呎 (2房)
 $1406万
 $23,918/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25610,7 +25610,7 @@
           <t>B | 496呎 (2房)
 $1306万
 $26,323/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -25618,7 +25618,7 @@
           <t>C | 591呎 (2房)
 $1552万
 $26,257/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -25626,7 +25626,7 @@
           <t>D | 448呎 (2房)
 $977万
 $21,806/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -25634,7 +25634,7 @@
           <t>E | 453呎 (2房)
 $1001万
 $22,104/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -25642,7 +25642,7 @@
           <t>F | 505呎 (2房)
 $1271万
 $25,160/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -25650,7 +25650,7 @@
           <t>G | 498呎 (2房)
 $1258万
 $25,253/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25658,7 +25658,7 @@
           <t>H | 494呎 (2房)
 $1108万
 $22,425/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr"/>
@@ -25668,7 +25668,7 @@
           <t>P1 | 1294呎 (4+房)
 $4917万
 $38,000/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -25691,7 +25691,7 @@
           <t>A | 588呎 (2房)
 $1466万
 $24,927/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25699,7 +25699,7 @@
           <t>B | 496呎 (2房)
 $1294万
 $26,089/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -25707,7 +25707,7 @@
           <t>C | 591呎 (2房)
 $1529万
 $25,868/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -25715,7 +25715,7 @@
           <t>D | 448呎 (2房)
 $970万
 $21,654/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -25723,7 +25723,7 @@
           <t>E | 453呎 (2房)
 $1004万
 $22,161/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -25731,7 +25731,7 @@
           <t>F | 505呎 (2房)
 $1192万
 $23,608/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>G | 498呎 (2房)
 $1249万
 $25,076/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25747,7 +25747,7 @@
           <t>H | 494呎 (2房)
 $1098万
 $22,225/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
           <t>P1 | 1294呎 (4+房)
 $5112万
 $39,505/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -25765,7 +25765,7 @@
           <t>P2 | 1158呎 (4+房)
 $4635万
 $40,022/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
           <t>A | 588呎 (2房)
 $1455万
 $24,740/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25788,7 +25788,7 @@
           <t>B | 496呎 (2房)
 $1275万
 $25,700/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -25796,7 +25796,7 @@
           <t>C | 591呎 (2房)
 $1515万
 $25,636/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -25804,7 +25804,7 @@
           <t>D | 448呎 (2房)
 $1012万
 $22,578/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -25812,7 +25812,7 @@
           <t>E | 453呎 (2房)
 $996万
 $21,987/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -25820,7 +25820,7 @@
           <t>F | 505呎 (2房)
 $1183万
 $23,422/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -25828,7 +25828,7 @@
           <t>G | 498呎 (2房)
 $1183万
 $23,751/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25836,7 +25836,7 @@
           <t>H | 494呎 (2房)
 $1088万
 $22,026/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr"/>
@@ -25846,7 +25846,7 @@
           <t>P1 | 1294呎 (4+房)
 $4428万
 $34,219/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -25854,7 +25854,7 @@
           <t>P2 | 1158呎 (4+房)
 $4461万
 $38,522/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
           <t>A | 588呎 (2房)
 $1444万
 $24,556/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25877,7 +25877,7 @@
           <t>B | 496呎 (2房)
 $1225万
 $24,700/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -25885,7 +25885,7 @@
           <t>C | 591呎 (2房)
 $1502万
 $25,406/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -25893,7 +25893,7 @@
           <t>D | 448呎 (2房)
 $957万
 $21,355/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -25901,7 +25901,7 @@
           <t>E | 453呎 (2房)
 $988万
 $21,810/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -25909,7 +25909,7 @@
           <t>F | 505呎 (2房)
 $1173万
 $23,236/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -25917,7 +25917,7 @@
           <t>G | 498呎 (2房)
 $1175万
 $23,586/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>H | 494呎 (2房)
 $1132万
 $22,921/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr"/>
@@ -25935,7 +25935,7 @@
           <t>P1 | 1294呎 (4+房)
 $4859万
 $37,550/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -25943,7 +25943,7 @@
           <t>P2 | 1158呎 (4+房)
 $3972万
 $34,300/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
     </row>
@@ -25958,7 +25958,7 @@
           <t>A | 586呎 (2房)
 $1360万
 $23,213/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25966,7 +25966,7 @@
           <t>B | 497呎 (2房)
 $1315万
 $26,467/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -25974,7 +25974,7 @@
           <t>C | 591呎 (2房)
 $1488万
 $25,181/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -25982,7 +25982,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,266/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -25990,7 +25990,7 @@
           <t>E | 453呎 (2房)
 $980万
 $21,638/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -25998,7 +25998,7 @@
           <t>F | 505呎 (2房)
 $1164万
 $23,050/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -26006,7 +26006,7 @@
           <t>G | 502呎 (2房)
 $1140万
 $22,713/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -26014,7 +26014,7 @@
           <t>H | 498呎 (2房)
 $1071万
 $21,508/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>J | 480呎 (2房)
 $1030万
 $21,460/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>K | 507呎 (2房)
 $1152万
 $22,714/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -26038,7 +26038,7 @@
           <t>P1 | 778呎 (3房)
 $2287万
 $29,400/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -26046,7 +26046,7 @@
           <t>P2 | 759呎 (3房)
 $2209万
 $29,100/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26061,7 @@
           <t>A | 586呎 (2房)
 $1350万
 $23,039/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>B | 497呎 (2房)
 $1243万
 $25,018/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -26077,7 +26077,7 @@
           <t>C | 591呎 (2房)
 $1430万
 $24,200/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -26085,7 +26085,7 @@
           <t>D | 448呎 (2房)
 $992万
 $22,154/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -26093,7 +26093,7 @@
           <t>E | 453呎 (2房)
 $975万
 $21,530/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -26101,7 +26101,7 @@
           <t>F | 505呎 (2房)
 $1158万
 $22,937/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -26109,7 +26109,7 @@
           <t>G | 502呎 (2房)
 $1170万
 $23,307/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -26117,7 +26117,7 @@
           <t>H | 498呎 (2房)
 $1119万
 $22,470/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -26125,7 +26125,7 @@
           <t>J | 480呎 (2房)
 $1035万
 $21,558/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>K | 507呎 (2房)
 $1146万
 $22,600/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>P1 | 778呎 (3房)
 $2264万
 $29,100/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>P2 | 759呎 (3房)
 $2391万
 $31,501/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -26164,7 +26164,7 @@
           <t>A | 586呎 (2房)
 $1338万
 $22,834/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -26172,7 +26172,7 @@
           <t>B | 497呎 (2房)
 $1198万
 $24,115/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -26180,7 +26180,7 @@
           <t>C | 591呎 (2房)
 $1493万
 $25,259/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -26188,7 +26188,7 @@
           <t>D | 448呎 (2房)
 $988万
 $22,045/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -26196,7 +26196,7 @@
           <t>E | 453呎 (2房)
 $970万
 $21,422/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -26204,7 +26204,7 @@
           <t>F | 505呎 (2房)
 $1152万
 $22,822/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -26212,7 +26212,7 @@
           <t>G | 502呎 (2房)
 $1164万
 $23,189/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -26220,7 +26220,7 @@
           <t>H | 498呎 (2房)
 $1060万
 $21,293/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -26228,7 +26228,7 @@
           <t>J | 480呎 (2房)
 $1068万
 $22,254/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -26236,7 +26236,7 @@
           <t>K | 507呎 (2房)
 $1140万
 $22,487/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -26244,7 +26244,7 @@
           <t>P1 | 778呎 (3房)
 $2241万
 $28,799/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -26252,7 +26252,7 @@
           <t>P2 | 759呎 (3房)
 $2194万
 $28,900/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -26267,7 +26267,7 @@
           <t>A | 586呎 (2房)
 $1326万
 $22,631/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>B | 497呎 (2房)
 $1191万
 $23,972/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>C | 591呎 (2房)
 $1413万
 $23,912/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -26291,7 +26291,7 @@
           <t>D | 448呎 (2房)
 $936万
 $20,891/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -26299,7 +26299,7 @@
           <t>E | 453呎 (2房)
 $1014万
 $22,382/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -26307,7 +26307,7 @@
           <t>F | 505呎 (2房)
 $1147万
 $22,709/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -26315,7 +26315,7 @@
           <t>G | 502呎 (2房)
 $1179万
 $23,494/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -26323,7 +26323,7 @@
           <t>H | 498呎 (2房)
 $1108万
 $22,247/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -26331,7 +26331,7 @@
           <t>J | 480呎 (2房)
 $1063万
 $22,144/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -26339,7 +26339,7 @@
           <t>K | 507呎 (2房)
 $1134万
 $22,375/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -26347,7 +26347,7 @@
           <t>P1 | 778呎 (3房)
 $2217万
 $28,500/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -26355,7 +26355,7 @@
           <t>P2 | 759呎 (3房)
 $2155万
 $28,395/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -26370,7 +26370,7 @@
           <t>A | 586呎 (2房)
 $1377万
 $23,502/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>B | 497呎 (2房)
 $1244万
 $25,020/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>C | 591呎 (2房)
 $1405万
 $23,770/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>D | 448呎 (2房)
 $931万
 $20,786/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,272/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>F | 505呎 (2房)
 $1141万
 $22,596/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -26418,7 +26418,7 @@
           <t>G | 502呎 (2房)
 $1174万
 $23,376/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -26426,7 +26426,7 @@
           <t>H | 498呎 (2房)
 $1050万
 $21,082/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -26434,7 +26434,7 @@
           <t>J | 480呎 (2房)
 $1007万
 $20,983/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -26442,7 +26442,7 @@
           <t>K | 507呎 (2房)
 $1129万
 $22,264/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -26450,7 +26450,7 @@
           <t>P1 | 778呎 (3房)
 $2194万
 $28,201/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -26458,7 +26458,7 @@
           <t>P2 | 759呎 (3房)
 $2221万
 $29,264/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
           <t>A | 586呎 (2房)
 $1305万
 $22,271/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>B | 497呎 (2房)
 $1177万
 $23,686/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>C | 591呎 (2房)
 $1396万
 $23,628/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>D | 448呎 (2房)
 $927万
 $20,683/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>E | 453呎 (2房)
 $956万
 $21,104/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>F | 505呎 (2房)
 $1135万
 $22,483/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>G | 502呎 (2房)
 $1112万
 $22,153/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>H | 498呎 (2房)
 $1097万
 $22,026/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>J | 480呎 (2房)
 $1002万
 $20,879/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -26545,7 +26545,7 @@
           <t>K | 507呎 (2房)
 $1123万
 $22,154/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -26553,7 +26553,7 @@
           <t>P1 | 778呎 (3房)
 $2293万
 $29,474/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -26561,7 +26561,7 @@
           <t>P2 | 759呎 (3房)
 $2273万
 $29,950/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
           <t>A | 586呎 (2房)
 $1299万
 $22,160/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>B | 497呎 (2房)
 $1157万
 $23,274/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>C | 591呎 (2房)
 $1388万
 $23,486/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>D | 448呎 (2房)
 $922万
 $20,580/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>E | 453呎 (2房)
 $951万
 $21,000/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>F | 505呎 (2房)
 $1130万
 $22,370/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>G | 502呎 (2房)
 $1107万
 $22,044/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,873/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>J | 480呎 (2房)
 $997万
 $20,775/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>K | 507呎 (2房)
 $1118万
 $22,043/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P1 | 778呎 (3房)
 $2129万
 $27,361/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>P2 | 759呎 (3房)
 $2121万
 $27,947/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 586呎 (2房)
 $1357万
 $23,152/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 497呎 (2房)
 $1139万
 $22,909/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 591呎 (2房)
 $1380万
 $23,347/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 448呎 (2房)
 $963万
 $21,502/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 453呎 (2房)
 $994万
 $21,938/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 505呎 (2房)
 $1124万
 $22,259/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 502呎 (2房)
 $1101万
 $21,934/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 498呎 (2房)
 $1034万
 $20,769/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 480呎 (2房)
 $992万
 $20,673/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 507呎 (2房)
 $1168万
 $23,030/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>P1 | 778呎 (3房)
 $2112万
 $27,144/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>P2 | 759呎 (3房)
 $2032万
 $26,771/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -26782,7 +26782,7 @@
           <t>A | 586呎 (2房)
 $1286万
 $21,940/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -26790,7 +26790,7 @@
           <t>B | 497呎 (2房)
 $1184万
 $23,817/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -26798,7 +26798,7 @@
           <t>C | 591呎 (2房)
 $1372万
 $23,208/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -26806,7 +26806,7 @@
           <t>D | 448呎 (2房)
 $913万
 $20,375/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>E | 453呎 (2房)
 $942万
 $20,792/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>F | 505呎 (2房)
 $1118万
 $22,149/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>G | 502呎 (2房)
 $1096万
 $21,825/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>H | 498呎 (2房)
 $1029万
 $20,667/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>J | 480呎 (2房)
 $987万
 $20,569/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>K | 507呎 (2房)
 $1106万
 $21,824/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>P1 | 778呎 (3房)
 $2095万
 $26,929/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>P2 | 759呎 (3房)
 $2016万
 $26,557/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26885,7 @@
           <t>A | 586呎 (2房)
 $1279万
 $21,831/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -26893,7 +26893,7 @@
           <t>B | 497呎 (2房)
 $1116万
 $22,459/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -26901,7 +26901,7 @@
           <t>C | 591呎 (2房)
 $1363万
 $23,069/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -26909,7 +26909,7 @@
           <t>D | 448呎 (2房)
 $908万
 $20,275/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -26917,7 +26917,7 @@
           <t>E | 453呎 (2房)
 $937万
 $20,689/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -26925,7 +26925,7 @@
           <t>F | 505呎 (2房)
 $1155万
 $22,865/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -26933,7 +26933,7 @@
           <t>G | 502呎 (2房)
 $1090万
 $21,715/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>H | 498呎 (2房)
 $1024万
 $20,562/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>J | 480呎 (2房)
 $982万
 $20,467/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>K | 507呎 (2房)
 $1156万
 $22,801/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>P1 | 778呎 (3房)
 $2078万
 $26,715/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>P2 | 759呎 (3房)
 $2000万
 $26,347/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -26988,7 +26988,7 @@
           <t>A | 586呎 (2房)
 $1273万
 $21,722/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -26996,7 +26996,7 @@
           <t>B | 497呎 (2房)
 $1105万
 $22,237/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -27004,7 +27004,7 @@
           <t>C | 591呎 (2房)
 $1322万
 $22,372/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27012,7 +27012,7 @@
           <t>D | 448呎 (2房)
 $904万
 $20,174/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -27020,7 +27020,7 @@
           <t>E | 453呎 (2房)
 $979万
 $21,614/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -27028,7 +27028,7 @@
           <t>F | 505呎 (2房)
 $1107万
 $21,929/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -27036,7 +27036,7 @@
           <t>G | 502呎 (2房)
 $1085万
 $21,608/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -27044,7 +27044,7 @@
           <t>H | 498呎 (2房)
 $1070万
 $21,484/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -27052,7 +27052,7 @@
           <t>J | 480呎 (2房)
 $1026万
 $21,383/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -27060,7 +27060,7 @@
           <t>K | 507呎 (2房)
 $1150万
 $22,688/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>P1 | 778呎 (3房)
 $2156万
 $27,719/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>P2 | 759呎 (3房)
 $2075万
 $27,336/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
           <t>A | 586呎 (2房)
 $1267万
 $21,614/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -27099,7 +27099,7 @@
           <t>B | 497呎 (2房)
 $1094万
 $22,016/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -27107,7 +27107,7 @@
           <t>C | 591呎 (2房)
 $1316万
 $22,261/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27115,7 +27115,7 @@
           <t>D | 448呎 (2房)
 $899万
 $20,074/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27123,7 +27123,7 @@
           <t>E | 453呎 (2房)
 $974万
 $21,508/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -27131,7 +27131,7 @@
           <t>F | 505呎 (2房)
 $1102万
 $21,820/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -27139,7 +27139,7 @@
           <t>G | 502呎 (2房)
 $1079万
 $21,500/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -27147,7 +27147,7 @@
           <t>H | 498呎 (2房)
 $1014万
 $20,359/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -27155,7 +27155,7 @@
           <t>J | 480呎 (2房)
 $973万
 $20,265/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -27163,7 +27163,7 @@
           <t>K | 507呎 (2房)
 $1144万
 $22,574/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -27171,7 +27171,7 @@
           <t>P1 | 778呎 (3房)
 $2038万
 $26,189/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -27179,7 +27179,7 @@
           <t>P2 | 759呎 (3房)
 $1960万
 $25,829/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
           <t>A | 586呎 (2房)
 $1260万
 $21,507/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -27202,7 +27202,7 @@
           <t>B | 497呎 (2房)
 $1055万
 $21,219/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -27210,7 +27210,7 @@
           <t>C | 591呎 (2房)
 $1374万
 $23,257/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27218,7 +27218,7 @@
           <t>D | 448呎 (2房)
 $895万
 $19,973/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27226,7 +27226,7 @@
           <t>E | 453呎 (2房)
 $923万
 $20,380/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -27234,7 +27234,7 @@
           <t>F | 505呎 (2房)
 $1096万
 $21,711/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
@@ -27242,7 +27242,7 @@
           <t>G | 502呎 (2房)
 $1074万
 $21,394/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -27250,7 +27250,7 @@
           <t>H | 498呎 (2房)
 $1009万
 $20,257/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -27258,7 +27258,7 @@
           <t>J | 480呎 (2房)
 $968万
 $20,162/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -27266,7 +27266,7 @@
           <t>K | 507呎 (2房)
 $1085万
 $21,394/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -27274,7 +27274,7 @@
           <t>P1 | 778呎 (3房)
 $2186万
 $28,091/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -27282,7 +27282,7 @@
           <t>P2 | 759呎 (3房)
 $1945万
 $25,623/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
           <t>A | 586呎 (2房)
 $1254万
 $21,399/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -27305,7 +27305,7 @@
           <t>B | 497呎 (2房)
 $1102万
 $22,183/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -27313,7 +27313,7 @@
           <t>C | 591呎 (2房)
 $1303万
 $22,041/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -27321,7 +27321,7 @@
           <t>D | 448呎 (2房)
 $890万
 $19,875/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -27329,7 +27329,7 @@
           <t>E | 453呎 (2房)
 $919万
 $20,280/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -27337,7 +27337,7 @@
           <t>F | 505呎 (2房)
 $1091万
 $21,604/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -27345,7 +27345,7 @@
           <t>G | 502呎 (2房)
 $1069万
 $21,287/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -27353,7 +27353,7 @@
           <t>H | 498呎 (2房)
 $1004万
 $20,157/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -27361,7 +27361,7 @@
           <t>J | 480呎 (2房)
 $963万
 $20,062/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -27369,7 +27369,7 @@
           <t>K | 507呎 (2房)
 $1079万
 $21,286/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -27377,7 +27377,7 @@
           <t>P1 | 778呎 (3房)
 $2077万
 $26,700/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -27385,7 +27385,7 @@
           <t>P2 | 759呎 (3房)
 $2163万
 $28,501/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
           <t>A | 586呎 (2房)
 $1248万
 $21,294/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -27408,7 +27408,7 @@
           <t>B | 497呎 (2房)
 $1110万
 $22,340/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -27416,7 +27416,7 @@
           <t>C | 591呎 (2房)
 $1296万
 $21,931/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -27424,7 +27424,7 @@
           <t>D | 448呎 (2房)
 $886万
 $19,777/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -27432,7 +27432,7 @@
           <t>E | 453呎 (2房)
 $960万
 $21,185/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -27440,7 +27440,7 @@
           <t>F | 505呎 (2房)
 $1140万
 $22,570/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -27448,7 +27448,7 @@
           <t>G | 502呎 (2房)
 $1063万
 $21,181/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -27456,7 +27456,7 @@
           <t>H | 498呎 (2房)
 $999万
 $20,056/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>J | 480呎 (2房)
 $958万
 $19,962/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -27472,7 +27472,7 @@
           <t>K | 507呎 (2房)
 $1074万
 $21,181/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -27480,7 +27480,7 @@
           <t>P1 | 778呎 (3房)
 $2140万
 $27,500/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -27488,7 +27488,7 @@
           <t>P2 | 759呎 (3房)
 $2148万
 $28,300/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
           <t>A | 586呎 (2房)
 $1238万
 $21,125/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>B | 497呎 (2房)
 $1049万
 $21,107/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>C | 591呎 (2房)
 $1290万
 $21,821/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>D | 448呎 (2房)
 $879万
 $19,618/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>E | 453呎 (2房)
 $907万
 $20,018/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>F | 505呎 (2房)
 $1077万
 $21,325/呎
-(25年-09月)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -27551,7 +27551,7 @@
           <t>G | 502呎 (2房)
 $1055万
 $21,012/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -27559,7 +27559,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,894/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -27567,7 +27567,7 @@
           <t>J | 480呎 (2房)
 $998万
 $20,794/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -27575,7 +27575,7 @@
           <t>K | 507呎 (2房)
 $1065万
 $21,014/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -27583,7 +27583,7 @@
           <t>P1 | 778呎 (3房)
 $2050万
 $26,350/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -27591,7 +27591,7 @@
           <t>P2 | 759呎 (3房)
 $2269万
 $29,900/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27607,7 @@
           <t>B | 509呎 (2房)
 $1066万
 $20,939/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -27615,7 +27615,7 @@
           <t>C | 591呎 (2房)
 $1347万
 $22,799/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -27623,7 +27623,7 @@
           <t>D | 448呎 (2房)
 $872万
 $19,464/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -27631,7 +27631,7 @@
           <t>E | 453呎 (2房)
 $945万
 $20,852/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -27639,7 +27639,7 @@
           <t>F | 505呎 (2房)
 $1068万
 $21,156/呎
-(25年-09月)</t>
+(25年-09月-24日)</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">
@@ -27647,7 +27647,7 @@
           <t>G | 502呎 (2房)
 $1046万
 $20,847/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -27655,7 +27655,7 @@
           <t>H | 505呎 (2房)
 $1047万
 $20,727/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -27663,7 +27663,7 @@
           <t>J | 480呎 (2房)
 $943万
 $19,648/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
@@ -27671,7 +27671,7 @@
           <t>K | 507呎 (2房)
 $1057万
 $20,846/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
@@ -27679,7 +27679,7 @@
           <t>P1 | 778呎 (3房)
 $2150万
 $27,640/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
@@ -27687,7 +27687,7 @@
           <t>P2 | 759呎 (3房)
 $2429万
 $32,000/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
           <t>B | 509呎 (2房)
 $1110万
 $21,811/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 591呎 (2房)
 $1277万
 $21,604/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 402呎 (2房)
 $1199万
 $29,818/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 407呎 (2房)
 $1188万
 $29,194/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 459呎 (2房)
 $1249万
 $27,207/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="H39" s="22" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 455呎 (2房)
 $1356万
 $29,798/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 458呎 (2房)
 $1319万
 $28,799/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 433呎 (2房)
 $1241万
 $28,656/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="K39" s="22" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 460呎 (2房)
 $1329万
 $28,887/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>P1 | 778呎 (3房)
 $2473万
 $31,789/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="M39" s="22" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>P2 | 759呎 (3房)
 $2520万
 $33,200/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
